--- a/artfynd/A 6832-2024 artfynd.xlsx
+++ b/artfynd/A 6832-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 6832-2024 artfynd.xlsx
+++ b/artfynd/A 6832-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>68597904</v>
+        <v>68597690</v>
       </c>
       <c r="B2" t="n">
-        <v>4711</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>513240.090410939</v>
+        <v>513160</v>
       </c>
       <c r="R2" t="n">
-        <v>6698812.892011618</v>
+        <v>6698845</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,24 +752,14 @@
           <t>2017-06-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-06-04</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Torrgran 30cm,12-15m.</t>
+          <t>Torrgran 50cm,15m.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,15 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>68597690</v>
+        <v>68597904</v>
       </c>
       <c r="B3" t="n">
-        <v>4711</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -854,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513159.8452599335</v>
+        <v>513240</v>
       </c>
       <c r="R3" t="n">
-        <v>6698845.191067315</v>
+        <v>6698813</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,24 +867,14 @@
           <t>2017-06-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-06-04</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Torrgran 50cm,15m.</t>
+          <t>Torrgran 30cm,12-15m.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -938,12 +908,7 @@
         <v>68597897</v>
       </c>
       <c r="B4" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513240.090410939</v>
+        <v>513240</v>
       </c>
       <c r="R4" t="n">
-        <v>6698812.892011618</v>
+        <v>6698813</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,19 +982,9 @@
           <t>2017-06-04</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-06-04</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1068,12 +1023,7 @@
         <v>68597743</v>
       </c>
       <c r="B5" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513159.8452599335</v>
+        <v>513160</v>
       </c>
       <c r="R5" t="n">
-        <v>6698845.191067315</v>
+        <v>6698845</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1147,19 +1097,9 @@
           <t>2017-06-04</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2017-06-04</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1198,12 +1138,7 @@
         <v>68597886</v>
       </c>
       <c r="B6" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>513240.090410939</v>
+        <v>513240</v>
       </c>
       <c r="R6" t="n">
-        <v>6698812.892011618</v>
+        <v>6698813</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1277,19 +1212,9 @@
           <t>2017-06-04</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2017-06-04</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">

--- a/artfynd/A 6832-2024 artfynd.xlsx
+++ b/artfynd/A 6832-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -787,6 +792,11 @@
           <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68597690</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
           <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68597904</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,6 +1032,11 @@
           <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68597897</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1132,6 +1152,11 @@
           <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68597743</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1247,8 +1272,20 @@
           <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68597886</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>